--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_430_Liberia.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_430_Liberia.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R63d4633aa4554c5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R8ec58fa0608e437b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Ra60dfcf3ad6e443d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R95c98e50fa7f4f0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Re130afe4594b417d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Ra73f58f9a88a48f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R4ef3a8737ad548cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R1607dfb8fbf44610"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R35b8f230ad074b5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Ra122a85f499546e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R3627cba80ae1475d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R043ea3958b7b4426"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ430CommercialTable" displayName="EEZ430CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ430CommercialTable" displayName="EEZ430CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ430FunctionalTable" displayName="EEZ430FunctionalTable" ref="A1:O26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O26"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ430FunctionalTable" displayName="EEZ430FunctionalTable" ref="A1:E26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E26"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ430ValidationTable" displayName="EEZ430ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ430ValidationTable" displayName="EEZ430ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -16707,7 +16661,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31322d7f92004d23"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc57e756821b04aff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16717,20 +16671,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -16738,660 +16682,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>72.353545035</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>72.353545035</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$240,A2,'Species'!$U$2:$U$240))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>9320.94219547477</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>9320.94219547477</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>615.7526449077001</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.440284568213374</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2756.0339824943235</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>615.7526449077001</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2825.6638937546386</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$240,A3,'Species'!$U$2:$U$240))</x:f>
-        <x:v>1739910.016199609</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.440284568213374</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2756.0339824943235</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1697035.2141763817</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>42874.80202322733</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0252645329130874</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.025264532913087286</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1613.4915065321</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.365745244618433</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>232.13746879161874</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1613.4915065321</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>296.8857109699079</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$240,A4,'Species'!$U$2:$U$240))</x:f>
-        <x:v>479022.5730606903</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.365745244618433</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>232.13746879161874</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>374551.8342431373</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>104470.73881755304</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.2789219789262511</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.2789219789262511</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>2650.9198149613</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.365951590046025</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>232.24778998723636</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>2650.9198149613</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>245.84370987544852</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$240,A5,'Species'!$U$2:$U$240))</x:f>
-        <x:v>651711.9618924235</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.365951590046025</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>232.24778998723636</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>615670.2684581354</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>36041.69343428803</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0585405780996209</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.05854057809962088</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>2579.7100449045</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.0302148214773923</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>107.20494577243988</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>2579.7100449045</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>183.58177933933894</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$240,A6,'Species'!$U$2:$U$240))</x:f>
-        <x:v>473587.7602231341</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.0302148214773923</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>107.20494577243988</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>276557.6754726054</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>197030.08475052868</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.7124375934019074</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.7124375934019074</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1327.1882568627</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.7011388831652194</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>50.25032595017397</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1327.1882568627</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>79.32902491134</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$240,A7,'Species'!$U$2:$U$240))</x:f>
-        <x:v>105284.55029069903</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.7011388831652194</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>50.25032595017397</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>66691.6425045939</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>38592.907786105134</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.578676822713532</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.5786768227135319</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>98958.84677925767</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.2993638660977345</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>199.23418889962647</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>98958.84677925767</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>218.01971983616357</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$240,A8,'Species'!$U$2:$U$240))</x:f>
-        <x:v>21574980.050123595</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.2993638660977345</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>199.23418889962647</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>19715985.572507817</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>1858994.4776157774</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0942886913149288</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.0942886913149287</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>53126.48544101731</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.59938312576088</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>397.54209837861316</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>53126.48544101731</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>604.0392403306653</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$240,A9,'Species'!$U$2:$U$240))</x:f>
-        <x:v>32090481.907230243</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.59938312576088</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>397.54209837861316</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>21120014.501702864</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>10970467.40552738</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.519434653070094</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.519434653070094</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>729.4440354391</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.7773848295627617</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>598.9420842582421</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>729.4440354391</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>610.9029476943895</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$240,A10,'Species'!$U$2:$U$240))</x:f>
-        <x:v>445619.5114278369</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.7773848295627617</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>598.9420842582421</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>436894.73093563755</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>8724.780492199352</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.019969983326452</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.019969983326451855</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>4687.1613853849985</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.968189346876269</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>929.371492625861</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>4687.1613853849985</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1346.2596368783759</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$240,A11,'Species'!$U$2:$U$240))</x:f>
-        <x:v>6310136.184678754</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.968189346876269</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>929.371492625861</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>4356114.172913555</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>1954022.0117651988</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.4485699718146428</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.44856997181464264</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>12681.739199904403</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.400700294674244</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2515.940085788983</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>12681.739199904403</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2555.6893288788838</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$240,A12,'Species'!$U$2:$U$240))</x:f>
-        <x:v>32410585.544820715</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.400700294674244</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2515.940085788983</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>31906496.010560993</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>504089.53425972164</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.015798962508853</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.015798962508853022</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec992647958f4bc1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d5c675e2d784e38"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17401,20 +16916,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -17422,1416 +16927,497 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>3006.1283298351004</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.8848405543480355</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>767.0798141374213</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>3006.1283298351004</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>879.046198858282</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$240,A2,'Species'!$U$2:$U$240))</x:f>
-        <x:v>2642525.6816217406</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.8848405543480355</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>767.0798141374213</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>2305940.3605231456</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>336585.3210985949</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1459644520130756</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.1459644520130756</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1118.1414406904</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.45</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>281.8382931264455</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1118.1414406904</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>281.8382931264455</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$240,A3,'Species'!$U$2:$U$240))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>315135.075118127</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.45</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>281.8382931264455</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>315135.075118127</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>3.2273705015</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.34</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2187.761623949552</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>3.2273705015</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$240,A4,'Species'!$U$2:$U$240))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>7060.717329448519</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.34</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>7060.717329448519</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>3371.0529042064995</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.1150104993039545</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1303.1982835947103</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>3371.0529042064995</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1499.0717624822305</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$240,A5,'Species'!$U$2:$U$240))</x:f>
-        <x:v>5053450.218529679</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.1150104993039545</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1303.1982835947103</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>4393150.358668874</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>660299.8598608049</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.1503021308063939</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.1503021308063938</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>3524.0952840845</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.797489546850126</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>627.3205966553419</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>3524.0952840845</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>634.1226257940651</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$240,A6,'Species'!$U$2:$U$240))</x:f>
-        <x:v>2234708.5550921448</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.797489546850126</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>627.3205966553419</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>2210737.556282165</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>23970.998809979763</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0108429871025904</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.010842987102590414</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>13825.016294343799</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.393600799519408</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2475.1458747183087</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>13825.016294343799</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2528.832451772434</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$240,A7,'Species'!$U$2:$U$240))</x:f>
-        <x:v>34961149.85141928</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.393600799519408</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2475.1458747183087</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>34218932.04885846</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>742217.8025608212</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0216902678757207</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.021690267875720613</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>1857.2383888747001</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.534150295322203</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>342.0978110568233</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>1857.2383888747001</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>481.3769230743633</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$240,A8,'Species'!$U$2:$U$240))</x:f>
-        <x:v>894031.701052091</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.534150295322203</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>342.0978110568233</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>635357.187444736</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>258674.51360735495</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.4071324267970995</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.4071324267970994</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>2143.6587752080004</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.8338436436229357</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>682.0930801452178</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>2143.6587752080004</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>775.1420755294056</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$240,A9,'Species'!$U$2:$U$240))</x:f>
-        <x:v>1661640.112241553</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.8338436436229357</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>682.0930801452178</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1462174.81676195</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>199465.29547960288</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1364168587729664</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.13641685877296633</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>2790.6361150065</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.257282094596839</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1808.3483515218431</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>2790.6361150065</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1927.999190873719</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$240,A10,'Species'!$U$2:$U$240))</x:f>
-        <x:v>5380344.17175551</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.257282094596839</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1808.3483515218431</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>5046442.218269325</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>333901.9534861855</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.066165813268877</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.066165813268877</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>468.4223728695</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.585928949310947</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>385.41529846560377</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>468.4223728695</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>542.6562160574082</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$240,A11,'Species'!$U$2:$U$240))</x:f>
-        <x:v>254192.31237799523</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.585928949310947</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>385.41529846560377</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>180537.1486474647</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>73655.16373053053</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.407977883124526</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.40797788312452604</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>730.5313294924999</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.401547725113698</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2520.854183947026</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>730.5313294924999</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2654.5101722368277</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$240,A12,'Species'!$U$2:$U$240))</x:f>
-        <x:v>1939202.8452755348</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.401547725113698</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2520.854183947026</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>1841562.9584555519</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>97639.8868199829</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0530201187918493</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.053020118791849355</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>384.1437155604</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.08099300549109</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1205.0165328796459</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>384.1437155604</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1205.6290583441387</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$240,A13,'Species'!$U$2:$U$240))</x:f>
-        <x:v>463134.8260599037</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.08099300549109</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1205.0165328796459</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>462899.52825209807</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>235.2978078056476</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0005083129133747</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.0005083129133748067</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>1720.3553727656001</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.544065571626597</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>349.99800722583456</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>1720.3553727656001</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>476.8338500160582</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$240,A14,'Species'!$U$2:$U$240))</x:f>
-        <x:v>820323.675791632</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.544065571626597</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>349.99800722583456</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>602120.9521882178</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>218202.72360341426</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.3623901855772094</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.36239018557720937</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>88605.87493741627</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.287080834083001</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>193.6782418588192</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>88605.87493741627</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>198.09041764251594</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$240,A15,'Species'!$U$2:$U$240))</x:f>
-        <x:v>17551974.771933325</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.287080834083001</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>193.6782418588192</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>17161030.076241195</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>390944.69569212943</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0227809574340982</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.022780957434098185</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>24151.233622615397</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.6777457135878864</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>476.15211044247246</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>24151.233622615397</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>604.8989822467835</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$240,A16,'Species'!$U$2:$U$240))</x:f>
-        <x:v>14609056.638324352</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.6777457135878864</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>476.15211044247246</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>11499660.85919752</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>3109395.7791268323</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.27039021560709</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.2703902156070901</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>2479.8497392558</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>4.024695517594888</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>1058.5113462122606</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>2479.8497392558</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>1131.1500250478184</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$240,A17,'Species'!$U$2:$U$240))</x:f>
-        <x:v>2805082.0946740243</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>4.024695517594888</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>1058.5113462122606</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>2624949.0859037805</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>180133.00877024373</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.068623429588625</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.06862342958862504</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>1327.2142120019</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.701133580745014</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>50.24971243393512</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>1327.2142120019</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>79.32799990402249</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$240,A18,'Species'!$U$2:$U$240))</x:f>
-        <x:v>105285.248882304</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.701133580745014</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>50.24971243393512</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>66692.13249132728</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>38593.11639097672</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.578675699056338</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.5786756990563379</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>1145.0691336625998</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.275672977025852</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>188.65702300781646</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>1145.0691336625998</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>196.34645112086528</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$240,A19,'Species'!$U$2:$U$240))</x:f>
-        <x:v>224830.2606826952</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.275672977025852</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>188.65702300781646</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>216025.33389492557</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>8804.926787769626</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0407587694878988</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.04075876948789872</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small bathypelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>31.158400019899997</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>4.28</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>1905.4607179632483</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>31.158400019899997</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>1905.4607179632483</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$240,A20,'Species'!$U$2:$U$240))</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>59371.107272504734</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>4.28</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>1905.4607179632483</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
-        <x:v>59371.107272504734</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>15074.0411160472</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.0690425403613997</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>117.23101909923336</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>15074.0411160472</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>135.66705017077885</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$240,A21,'Species'!$U$2:$U$240))</x:f>
-        <x:v>2045050.6923671588</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.0690425403613997</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>117.23101909923336</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>1767145.2019779582</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>277905.4903892006</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.1572623970447602</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.1572623970447602</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>8594.705312915099</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.2533236201832567</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>179.19406445392698</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>8594.705312915099</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>183.2560613880466</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$240,A22,'Species'!$U$2:$U$240))</x:f>
-        <x:v>1575031.8444357396</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.2533236201832567</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>179.19406445392698</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>1540120.177805017</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>34911.66663072258</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0226681444304422</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.022668144430442287</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>1.0917903685</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.7299999999999995</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>537.0317963702522</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>1.0917903685</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>537.0317963702527</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$240,A23,'Species'!$U$2:$U$240))</x:f>
-        <x:v>586.3261428552952</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.7299999999999995</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>537.0317963702522</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>586.3261428552947</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>4.547473508864641e-13</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.0000000000000007</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>7.755877107439429e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>2650.9198149613</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.365951590046025</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>232.24778998723636</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>2650.9198149613</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>245.84370987544852</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$240,A24,'Species'!$U$2:$U$240))</x:f>
-        <x:v>651711.9618924235</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.365951590046025</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>232.24778998723636</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>615670.2684581354</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>36041.69343428803</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.0585405780996209</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.05854057809962088</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>35.595579275</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.9500590835242133</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>891.37219647499</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>35.595579275</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>907.8483578234149</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$240,A25,'Species'!$U$2:$U$240))</x:f>
-        <x:v>32315.38819058193</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.9500590835242133</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>891.37219647499</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>31728.90968315638</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>586.4785074255487</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.018484042259318</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.018484042259318066</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>3.6913022288</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>3.97</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>933.2543007969915</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>3.6913022288</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>933.2543007969915</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$240,A26,'Species'!$U$2:$U$240))</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>3444.9236805691207</x:v>
       </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>3.97</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>933.2543007969915</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
-        <x:v>3444.9236805691207</x:v>
-      </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G26">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O26">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c58f9f49fca4eb8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R433ea3c9ece545da"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19006,7 +17592,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -19105,7 +17691,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>96290641.00214316</x:v>
+        <x:v>80575332.56567119</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -19119,7 +17705,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>96290641.00214317</x:v>
+        <x:v>89268475.32954851</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -19133,7 +17719,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-2.9802322387695312e-8</x:v>
+        <x:v>-15715308.436471999</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -19147,7 +17733,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-1.4901161193847656e-8</x:v>
+        <x:v>-7022165.672594681</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -19158,9 +17744,9 @@
         <x:v>EEZ_430</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -19172,47 +17758,19 @@
         <x:v>EEZ_430</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_430</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_430</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15b5354d493d4374"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9367ad92f8964f5f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19259,7 +17817,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
